--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>314</v>
+        <v>424</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>310</v>
+        <v>405</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>0</v>
